--- a/code/data/combined/cmb+pelg+jmul-w0wacdm-fixed.xlsx
+++ b/code/data/combined/cmb+pelg+jmul-w0wacdm-fixed.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -477,28 +477,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39309903.7090937</v>
+        <v>47085114.32251151</v>
       </c>
       <c r="C2" t="n">
-        <v>-134472624.5712827</v>
+        <v>-157261959.8944202</v>
       </c>
       <c r="D2" t="n">
-        <v>40498344.88702374</v>
+        <v>49329327.98914728</v>
       </c>
       <c r="E2" t="n">
-        <v>-328826.7714335308</v>
+        <v>-398414.6565271034</v>
       </c>
       <c r="F2" t="n">
-        <v>-1339492.473741736</v>
+        <v>-1360014.498154846</v>
       </c>
       <c r="G2" t="n">
-        <v>879085.3645065371</v>
+        <v>1128429.193536058</v>
       </c>
       <c r="H2" t="n">
-        <v>6316971.330837872</v>
+        <v>7691729.910853918</v>
       </c>
       <c r="I2" t="n">
-        <v>1706714.956562276</v>
+        <v>2078929.533151345</v>
       </c>
     </row>
     <row r="3">
@@ -508,28 +508,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-134472624.5637163</v>
+        <v>-157261959.9101609</v>
       </c>
       <c r="C3" t="n">
-        <v>887787810.4869995</v>
+        <v>950153575.5939224</v>
       </c>
       <c r="D3" t="n">
-        <v>-89236526.51862</v>
+        <v>-117099218.5827824</v>
       </c>
       <c r="E3" t="n">
-        <v>15622280.82603881</v>
+        <v>16778104.85852899</v>
       </c>
       <c r="F3" t="n">
-        <v>6725763.59801449</v>
+        <v>6809926.535197656</v>
       </c>
       <c r="G3" t="n">
-        <v>-3830849.07182473</v>
+        <v>-4709260.18018247</v>
       </c>
       <c r="H3" t="n">
-        <v>-24732459.78002074</v>
+        <v>-29149992.43913041</v>
       </c>
       <c r="I3" t="n">
-        <v>-6672907.634477769</v>
+        <v>-7870496.625767293</v>
       </c>
     </row>
     <row r="4">
@@ -539,28 +539,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>40498344.887846</v>
+        <v>49329327.98749536</v>
       </c>
       <c r="C4" t="n">
-        <v>-89236526.52963288</v>
+        <v>-117099218.5602375</v>
       </c>
       <c r="D4" t="n">
-        <v>48990351.07437497</v>
+        <v>58628444.20490742</v>
       </c>
       <c r="E4" t="n">
-        <v>921795.3901191152</v>
+        <v>891559.1369049551</v>
       </c>
       <c r="F4" t="n">
-        <v>-954046.0478432474</v>
+        <v>-991365.5993427548</v>
       </c>
       <c r="G4" t="n">
-        <v>971974.4851278095</v>
+        <v>1239887.704693543</v>
       </c>
       <c r="H4" t="n">
-        <v>6531917.674459537</v>
+        <v>8059041.832508631</v>
       </c>
       <c r="I4" t="n">
-        <v>1765079.687245076</v>
+        <v>2178343.489562899</v>
       </c>
     </row>
     <row r="5">
@@ -570,28 +570,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-328826.7711591844</v>
+        <v>-398414.6571678837</v>
       </c>
       <c r="C5" t="n">
-        <v>15622280.82527507</v>
+        <v>16778104.86034542</v>
       </c>
       <c r="D5" t="n">
-        <v>921795.3904346126</v>
+        <v>891559.1361773406</v>
       </c>
       <c r="E5" t="n">
-        <v>1030767.846386198</v>
+        <v>1134894.161581133</v>
       </c>
       <c r="F5" t="n">
-        <v>29917.8407505666</v>
+        <v>45279.17529685608</v>
       </c>
       <c r="G5" t="n">
-        <v>-77271.80250355796</v>
+        <v>-86085.7199795487</v>
       </c>
       <c r="H5" t="n">
-        <v>-271712.1492126245</v>
+        <v>-306675.5458225549</v>
       </c>
       <c r="I5" t="n">
-        <v>-72255.40758403801</v>
+        <v>-81729.54500117592</v>
       </c>
     </row>
     <row r="6">
@@ -601,28 +601,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1339492.473731013</v>
+        <v>-1360014.498109835</v>
       </c>
       <c r="C6" t="n">
-        <v>6725763.598072679</v>
+        <v>6809926.53488381</v>
       </c>
       <c r="D6" t="n">
-        <v>-954046.0478206518</v>
+        <v>-991365.5993115561</v>
       </c>
       <c r="E6" t="n">
-        <v>29917.84075349671</v>
+        <v>45279.17528921727</v>
       </c>
       <c r="F6" t="n">
-        <v>637642.8265058707</v>
+        <v>649399.2715893931</v>
       </c>
       <c r="G6" t="n">
-        <v>103899.4427331224</v>
+        <v>103298.4894180129</v>
       </c>
       <c r="H6" t="n">
-        <v>-13611.52147992904</v>
+        <v>-19242.55382863013</v>
       </c>
       <c r="I6" t="n">
-        <v>-2370.838422027397</v>
+        <v>-3906.165861583999</v>
       </c>
     </row>
     <row r="7">
@@ -632,28 +632,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>879085.3644785404</v>
+        <v>1128429.193613961</v>
       </c>
       <c r="C7" t="n">
-        <v>-3830849.0719717</v>
+        <v>-4709260.179953749</v>
       </c>
       <c r="D7" t="n">
-        <v>971974.4850712899</v>
+        <v>1239887.704829126</v>
       </c>
       <c r="E7" t="n">
-        <v>-77271.80251174947</v>
+        <v>-86085.71996126273</v>
       </c>
       <c r="F7" t="n">
-        <v>103899.4427330334</v>
+        <v>103298.4894158437</v>
       </c>
       <c r="G7" t="n">
-        <v>66769.24939202688</v>
+        <v>75396.24381645072</v>
       </c>
       <c r="H7" t="n">
-        <v>228801.4399409282</v>
+        <v>274767.5091585398</v>
       </c>
       <c r="I7" t="n">
-        <v>62469.54455092163</v>
+        <v>74916.15416778694</v>
       </c>
     </row>
     <row r="8">
@@ -663,28 +663,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6316971.330756627</v>
+        <v>7691729.911058124</v>
       </c>
       <c r="C8" t="n">
-        <v>-24732459.7811104</v>
+        <v>-29149992.43702573</v>
       </c>
       <c r="D8" t="n">
-        <v>6531917.674223118</v>
+        <v>8059041.833022067</v>
       </c>
       <c r="E8" t="n">
-        <v>-271712.1492602193</v>
+        <v>-306675.5457133295</v>
       </c>
       <c r="F8" t="n">
-        <v>-13611.5214810785</v>
+        <v>-19242.55383863827</v>
       </c>
       <c r="G8" t="n">
-        <v>228801.4399433473</v>
+        <v>274767.5091510937</v>
       </c>
       <c r="H8" t="n">
-        <v>1195073.79013903</v>
+        <v>1444235.776044646</v>
       </c>
       <c r="I8" t="n">
-        <v>323623.1395274246</v>
+        <v>391087.3564391269</v>
       </c>
     </row>
     <row r="9">
@@ -694,28 +694,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1706714.956540031</v>
+        <v>2078929.533207417</v>
       </c>
       <c r="C9" t="n">
-        <v>-6672907.634770953</v>
+        <v>-7870496.625200647</v>
       </c>
       <c r="D9" t="n">
-        <v>1765079.687180935</v>
+        <v>2178343.489702702</v>
       </c>
       <c r="E9" t="n">
-        <v>-72255.40759690457</v>
+        <v>-81729.54497163925</v>
       </c>
       <c r="F9" t="n">
-        <v>-2370.838422336039</v>
+        <v>-3906.165864301356</v>
       </c>
       <c r="G9" t="n">
-        <v>62469.5445515677</v>
+        <v>74916.15416579833</v>
       </c>
       <c r="H9" t="n">
-        <v>323623.1395273776</v>
+        <v>391087.3564392742</v>
       </c>
       <c r="I9" t="n">
-        <v>87740.08077312604</v>
+        <v>106007.1235805175</v>
       </c>
     </row>
   </sheetData>

--- a/code/data/combined/cmb+pelg+jmul-w0wacdm-fixed.xlsx
+++ b/code/data/combined/cmb+pelg+jmul-w0wacdm-fixed.xlsx
@@ -477,28 +477,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>47085114.32251151</v>
+        <v>43671284.58039773</v>
       </c>
       <c r="C2" t="n">
-        <v>-157261959.8944202</v>
+        <v>-146032037.9981689</v>
       </c>
       <c r="D2" t="n">
-        <v>49329327.98914728</v>
+        <v>45623756.27543603</v>
       </c>
       <c r="E2" t="n">
-        <v>-398414.6565271034</v>
+        <v>-379416.154186473</v>
       </c>
       <c r="F2" t="n">
-        <v>-1360014.498154846</v>
+        <v>-1334633.657543598</v>
       </c>
       <c r="G2" t="n">
-        <v>1128429.193536058</v>
+        <v>1020578.406729165</v>
       </c>
       <c r="H2" t="n">
-        <v>7691729.910853918</v>
+        <v>7086496.162354562</v>
       </c>
       <c r="I2" t="n">
-        <v>2078929.533151345</v>
+        <v>1915014.279919932</v>
       </c>
     </row>
     <row r="3">
@@ -508,28 +508,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-157261959.9101609</v>
+        <v>-146032037.9959799</v>
       </c>
       <c r="C3" t="n">
-        <v>950153575.5939224</v>
+        <v>876730590.700339</v>
       </c>
       <c r="D3" t="n">
-        <v>-117099218.5827824</v>
+        <v>-109841979.6464876</v>
       </c>
       <c r="E3" t="n">
-        <v>16778104.85852899</v>
+        <v>15993899.89158946</v>
       </c>
       <c r="F3" t="n">
-        <v>6809926.535197656</v>
+        <v>6606462.468071786</v>
       </c>
       <c r="G3" t="n">
-        <v>-4709260.18018247</v>
+        <v>-4341449.681194877</v>
       </c>
       <c r="H3" t="n">
-        <v>-29149992.43913041</v>
+        <v>-27073703.02168196</v>
       </c>
       <c r="I3" t="n">
-        <v>-7870496.625767293</v>
+        <v>-7308700.570688175</v>
       </c>
     </row>
     <row r="4">
@@ -539,28 +539,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>49329327.98749536</v>
+        <v>45623756.27559992</v>
       </c>
       <c r="C4" t="n">
-        <v>-117099218.5602375</v>
+        <v>-109841979.649584</v>
       </c>
       <c r="D4" t="n">
-        <v>58628444.20490742</v>
+        <v>53932634.06279211</v>
       </c>
       <c r="E4" t="n">
-        <v>891559.1369049551</v>
+        <v>816073.8808613172</v>
       </c>
       <c r="F4" t="n">
-        <v>-991365.5993427548</v>
+        <v>-974232.5064986148</v>
       </c>
       <c r="G4" t="n">
-        <v>1239887.704693543</v>
+        <v>1124804.267342818</v>
       </c>
       <c r="H4" t="n">
-        <v>8059041.832508631</v>
+        <v>7413155.221098811</v>
       </c>
       <c r="I4" t="n">
-        <v>2178343.489562899</v>
+        <v>2003334.662273359</v>
       </c>
     </row>
     <row r="5">
@@ -570,28 +570,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-398414.6571678837</v>
+        <v>-379416.1541090977</v>
       </c>
       <c r="C5" t="n">
-        <v>16778104.86034542</v>
+        <v>15993899.89144159</v>
       </c>
       <c r="D5" t="n">
-        <v>891559.1361773406</v>
+        <v>816073.8809624708</v>
       </c>
       <c r="E5" t="n">
-        <v>1134894.161581133</v>
+        <v>1110110.422574448</v>
       </c>
       <c r="F5" t="n">
-        <v>45279.17529685608</v>
+        <v>48716.74950743222</v>
       </c>
       <c r="G5" t="n">
-        <v>-86085.7199795487</v>
+        <v>-84279.01038687547</v>
       </c>
       <c r="H5" t="n">
-        <v>-306675.5458225549</v>
+        <v>-299688.0399637031</v>
       </c>
       <c r="I5" t="n">
-        <v>-81729.54500117592</v>
+        <v>-79864.86057114968</v>
       </c>
     </row>
     <row r="6">
@@ -601,28 +601,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1360014.498109835</v>
+        <v>-1334633.657600771</v>
       </c>
       <c r="C6" t="n">
-        <v>6809926.53488381</v>
+        <v>6606462.468138847</v>
       </c>
       <c r="D6" t="n">
-        <v>-991365.5993115561</v>
+        <v>-974232.5065739905</v>
       </c>
       <c r="E6" t="n">
-        <v>45279.17528921727</v>
+        <v>48716.74950351579</v>
       </c>
       <c r="F6" t="n">
-        <v>649399.2715893931</v>
+        <v>634464.500105634</v>
       </c>
       <c r="G6" t="n">
-        <v>103298.4894180129</v>
+        <v>102551.1391753631</v>
       </c>
       <c r="H6" t="n">
-        <v>-19242.55382863013</v>
+        <v>-16443.53985669234</v>
       </c>
       <c r="I6" t="n">
-        <v>-3906.165861583999</v>
+        <v>-3118.524978704968</v>
       </c>
     </row>
     <row r="7">
@@ -632,28 +632,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1128429.193613961</v>
+        <v>1020578.406699635</v>
       </c>
       <c r="C7" t="n">
-        <v>-4709260.179953749</v>
+        <v>-4341449.681214021</v>
       </c>
       <c r="D7" t="n">
-        <v>1239887.704829126</v>
+        <v>1124804.267299806</v>
       </c>
       <c r="E7" t="n">
-        <v>-86085.71996126273</v>
+        <v>-84279.01039037434</v>
       </c>
       <c r="F7" t="n">
-        <v>103298.4894158437</v>
+        <v>102551.139176768</v>
       </c>
       <c r="G7" t="n">
-        <v>75396.24381645072</v>
+        <v>71761.94660724804</v>
       </c>
       <c r="H7" t="n">
-        <v>274767.5091585398</v>
+        <v>255272.1081174663</v>
       </c>
       <c r="I7" t="n">
-        <v>74916.15416778694</v>
+        <v>69639.76285446028</v>
       </c>
     </row>
     <row r="8">
@@ -663,28 +663,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7691729.911058124</v>
+        <v>7086496.162292702</v>
       </c>
       <c r="C8" t="n">
-        <v>-29149992.43702573</v>
+        <v>-27073703.02195541</v>
       </c>
       <c r="D8" t="n">
-        <v>8059041.833022067</v>
+        <v>7413155.220990936</v>
       </c>
       <c r="E8" t="n">
-        <v>-306675.5457133295</v>
+        <v>-299688.0399789654</v>
       </c>
       <c r="F8" t="n">
-        <v>-19242.55383863827</v>
+        <v>-16443.53984780661</v>
       </c>
       <c r="G8" t="n">
-        <v>274767.5091510937</v>
+        <v>255272.1081205553</v>
       </c>
       <c r="H8" t="n">
-        <v>1444235.776044646</v>
+        <v>1336089.048242684</v>
       </c>
       <c r="I8" t="n">
-        <v>391087.3564391269</v>
+        <v>361803.5278007452</v>
       </c>
     </row>
     <row r="9">
@@ -694,28 +694,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2078929.533207417</v>
+        <v>1915014.279902638</v>
       </c>
       <c r="C9" t="n">
-        <v>-7870496.625200647</v>
+        <v>-7308700.570760673</v>
       </c>
       <c r="D9" t="n">
-        <v>2178343.489702702</v>
+        <v>2003334.662243563</v>
       </c>
       <c r="E9" t="n">
-        <v>-81729.54497163925</v>
+        <v>-79864.8605753127</v>
       </c>
       <c r="F9" t="n">
-        <v>-3906.165864301356</v>
+        <v>-3118.52497629946</v>
       </c>
       <c r="G9" t="n">
-        <v>74916.15416579833</v>
+        <v>69639.76285528253</v>
       </c>
       <c r="H9" t="n">
-        <v>391087.3564392742</v>
+        <v>361803.5278006594</v>
       </c>
       <c r="I9" t="n">
-        <v>106007.1235805175</v>
+        <v>98077.60204753146</v>
       </c>
     </row>
   </sheetData>
